--- a/reports/archive/weekly/shadow_report_weekly_2026-07-11.xlsx
+++ b/reports/archive/weekly/shadow_report_weekly_2026-07-11.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week_at_a_glance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bucket_Trends" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setup_x_Regime" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outperformers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underperformers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Trades_History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Week_at_a_glance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bucket_Trends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Setup_x_Regime" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Outperformers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Underperformers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommendations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="All_Trades_History" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-11 00:13 IST</t>
+          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-11 06:22 IST</t>
         </is>
       </c>
     </row>

--- a/reports/archive/weekly/shadow_report_weekly_2026-07-11.xlsx
+++ b/reports/archive/weekly/shadow_report_weekly_2026-07-11.xlsx
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-11 06:22 IST</t>
+          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-11 06:24 IST</t>
         </is>
       </c>
     </row>

--- a/reports/archive/weekly/shadow_report_weekly_2026-07-11.xlsx
+++ b/reports/archive/weekly/shadow_report_weekly_2026-07-11.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Week_at_a_glance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bucket_Trends" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Setup_x_Regime" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Outperformers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Underperformers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Recommendations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="All_Trades_History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Week_at_a_glance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bucket_Trends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setup_x_Regime" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outperformers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underperformers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Trades_History" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-11 06:24 IST</t>
+          <t>This week: 2026-W28  |  Last week: 2026-W27  |  Generated: 2026-07-11 11:47 IST</t>
         </is>
       </c>
     </row>
